--- a/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9254193289</v>
+        <v>46157.93117531444</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93117531444</v>
+        <v>46157.93369732046</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93369732046</v>
+        <v>46157.93674259126</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93674259126</v>
+        <v>46158.28195703381</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28195703381</v>
+        <v>46158.29720237266</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29720237266</v>
+        <v>46158.29792356331</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29792356331</v>
+        <v>46158.33357192785</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33357192785</v>
+        <v>46158.37211620406</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37211620406</v>
+        <v>46158.37268549137</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
